--- a/toledo-tps/Toledo_TPS_8-26_Workbook.xlsx
+++ b/toledo-tps/Toledo_TPS_8-26_Workbook.xlsx
@@ -1244,7 +1244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2578,77 +2578,259 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr"/>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>SLA13</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>SLA Toledo Prep 6th St</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>824 6th St, Toledo, OH 43605</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>Refrigerated</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>Wed 8/26 only</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="inlineStr">
+        <is>
+          <t>SNAP 2275 E 55th St</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>Customer Delivery</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>SLA14</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>SLA Toledo Prep Consaul</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>2014 Consaul St, Toledo, OH 43605</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>Refrigerated</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>Wed 8/26 only</t>
+        </is>
+      </c>
+      <c r="O20" s="6" t="inlineStr">
+        <is>
+          <t>SNAP 2275 E 55th St</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>Customer Delivery</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr"/>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>-- RETURN --</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>2275 E 55th St, Cleveland, OH 44103</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J19" s="6" t="inlineStr">
+      <c r="J21" s="6" t="inlineStr">
         <is>
           <t>SNAP</t>
         </is>
       </c>
-      <c r="K19" s="6" t="inlineStr">
+      <c r="K21" s="6" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="L19" s="6" t="inlineStr"/>
-      <c r="M19" s="6" t="inlineStr">
+      <c r="L21" s="6" t="inlineStr"/>
+      <c r="M21" s="6" t="inlineStr">
         <is>
           <t>Return</t>
         </is>
       </c>
-      <c r="N19" s="6" t="inlineStr"/>
-      <c r="O19" s="6" t="inlineStr">
+      <c r="N21" s="6" t="inlineStr"/>
+      <c r="O21" s="6" t="inlineStr">
         <is>
           <t>SNAP 2275 E 55th St</t>
         </is>
       </c>
-      <c r="P19" s="6" t="inlineStr">
+      <c r="P21" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="inlineStr">
         <is>
           <t>Return / End</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>
       </c>
-      <c r="S19" s="6" t="inlineStr">
+      <c r="S21" s="6" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
@@ -2665,7 +2847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3297,85 +3479,127 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>SLA Toledo Prep 6th St</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>824 6th St, Toledo, OH</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>43605</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>143.2</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>SLA Toledo Prep Consaul</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>2014 Consaul St, Toledo, OH</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>43605</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>144.8</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>DEADHEAD BACK - south Toledo to SNAP E 55th</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr"/>
-      <c r="D19" s="7" t="inlineStr"/>
-      <c r="E19" s="7" t="n">
-        <v>118.7</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>255.1</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>140</v>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Outbound deadhead</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>122.1 mi</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2 h 24 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>In-Toledo stop to stop, 11 legs</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>14.3 mi</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>39 min</t>
-        </is>
-      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>DEADHEAD BACK - east Toledo to SNAP E 55th</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr"/>
+      <c r="E21" s="7" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>257.8</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>133</v>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Return deadhead</t>
+          <t>Outbound deadhead</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -3383,74 +3607,82 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>118.7 mi</t>
+          <t>122.1 mi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2 h 20 min</t>
+          <t>2 h 24 min</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>TOTAL MILES</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr"/>
-      <c r="C24" s="9" t="inlineStr"/>
-      <c r="D24" s="9" t="inlineStr"/>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>255.1 mi</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr"/>
-      <c r="G24" s="9" t="inlineStr"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>In-Toledo stop to stop, 13 legs</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>22.7 mi</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>62 min</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Drive time</t>
+          <t>Return deadhead</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>113.1 mi</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>5.38 h</t>
+          <t>2 h 13 min</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Stop time, 12 x 20 min</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>4.00 h</t>
-        </is>
-      </c>
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>TOTAL MILES</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr"/>
+      <c r="C26" s="9" t="inlineStr"/>
+      <c r="D26" s="9" t="inlineStr"/>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>257.8 mi</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr"/>
+      <c r="G26" s="9" t="inlineStr"/>
+      <c r="H26" s="9" t="n"/>
+      <c r="I26" s="9" t="n"/>
+      <c r="J26" s="9" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Load-out</t>
+          <t>Drive time</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -3460,34 +3692,31 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.00 h</t>
+          <t>5.64 h</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>TOTAL ON-DUTY / BILLABLE</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr"/>
-      <c r="C28" s="9" t="inlineStr"/>
-      <c r="D28" s="9" t="inlineStr"/>
-      <c r="E28" s="9" t="inlineStr"/>
-      <c r="F28" s="9" t="inlineStr"/>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>10.38 h</t>
-        </is>
-      </c>
-      <c r="H28" s="9" t="n"/>
-      <c r="I28" s="9" t="n"/>
-      <c r="J28" s="9" t="n"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Stop time, 14 x 20 min</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>4.67 h</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Yard out</t>
+          <t>Load-out</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -3497,31 +3726,34 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>03:36</t>
+          <t>1.00 h</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>First delivery</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>TOTAL ON-DUTY / BILLABLE</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr"/>
+      <c r="C30" s="9" t="inlineStr"/>
+      <c r="D30" s="9" t="inlineStr"/>
+      <c r="E30" s="9" t="inlineStr"/>
+      <c r="F30" s="9" t="inlineStr"/>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>11.31 h</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="n"/>
+      <c r="I30" s="9" t="n"/>
+      <c r="J30" s="9" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Last delivery complete</t>
+          <t>Yard out</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -3531,14 +3763,14 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>03:36</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Back at SNAP</t>
+          <t>First delivery</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -3548,7 +3780,41 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Last delivery complete</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Back at SNAP</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3587,7 +3853,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Leave this with the SNAP team. One school per pallet - do not mix schools on a pallet.</t>
+          <t>Leave this with the SNAP team. One school per pallet - do not mix schools on a pallet. 12 TPS pallets plus the SLA Toledo pallet.</t>
         </is>
       </c>
     </row>
@@ -4070,167 +4336,241 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr"/>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SLA Toledo Prep 6th St</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>824 6th St, Toledo, OH 43605</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>15</v>
+      </c>
+      <c r="G18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>STOP 13 / SLA 6TH ST / 9 CS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SLA Toledo Prep Consaul</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2014 Consaul St, Toledo, OH 43605</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>15</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>STOP 14 / SLA CONSAUL / 5 CS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr"/>
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="n">
-        <v>294</v>
-      </c>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="n">
-        <v>326.6</v>
-      </c>
-      <c r="H18" s="5" t="n">
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="n">
+        <v>308</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="n">
+        <v>342.1</v>
+      </c>
+      <c r="H20" s="5" t="n">
         <v>3230</v>
       </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>12 pallets</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>13 pallets</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>BUILD RULES</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-      <c r="H20" s="10" t="n"/>
-      <c r="I20" s="10" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>One school per pallet</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>Agreed on the 8/21 call. Do not consolidate or cross-load - the driver must not break down a pallet at a stop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Label every pallet</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>School number and name, case count, stop number. Marked and wrapped by SNAP.</t>
-        </is>
-      </c>
+      <c r="B22" s="11" t="inlineStr"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="10" t="n"/>
+      <c r="I22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Load reverse stop order</t>
+          <t>One school per pallet</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Stop 12 loads first, stop 1 last and nearest the door.</t>
+          <t>Agreed on the 8/21 call. Do not consolidate or cross-load - the driver must not break down a pallet at a stop.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Label every pallet</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>REFRIGERATED, not frozen. Product is pulled to thaw for Thursday 8/27 service.</t>
+          <t>School number and name, case count, stop number. Marked and wrapped by SNAP.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Case geometry</t>
+          <t>Load reverse stop order</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>16.0 x 13.3 x 9.0 in, 9 per layer on a 48x40 pallet (3 across x 3 deep), 1.11 cu ft per case.</t>
+          <t>Stop 14 loads first, stop 1 last and nearest the door. The SLA pallet double-stacks on a 33 in school pallet.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Truck fit</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>12 pallets = all 12 floor positions in a 26 ft reefer. Tallest pallet 51 in. No room for a 13th pallet.</t>
+          <t>REFRIGERATED, not frozen. Product is pulled to thaw for Thursday 8/27 service.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>MEAL BUILD - confirm all six components ship together</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="10" t="n"/>
-      <c r="F27" s="10" t="n"/>
-      <c r="G27" s="10" t="n"/>
-      <c r="H27" s="10" t="n"/>
-      <c r="I27" s="10" t="n"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Case geometry</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>16.0 x 13.3 x 9.0 in, 9 per layer on a 48x40 pallet (3 across x 3 deep), 1.11 cu ft per case.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1. Beef Patty 2. Hamburger Bun 3. Tater Tots</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr"/>
+          <t>Truck fit</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>12 school pallets on the floor plus the SLA pallet double-stacked. Ten school pallets are 33 in, SLA is 24 in - 57 in stacked against ~90 in interior. Total cube 342 cu ft of ~1,600.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>4. Baked Beans 5. Watermelon Applesauce 6. Ketchup &amp; Mustard PC</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr"/>
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>MEAL BUILD - confirm all six components ship together</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
+      <c r="I29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>Read off the SNAP Production Inventory Request Form dated Fri 8/21 for Mon 8/24 delivery.</t>
-        </is>
-      </c>
+          <t>1. Beef Patty 2. Hamburger Bun 3. Tater Tots</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>4. Baked Beans 5. Watermelon Applesauce 6. Ketchup &amp; Mustard PC</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>Read off the SNAP Production Inventory Request Form dated Fri 8/21 for Mon 8/24 delivery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>No milk, no breakfast items</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Per Sean on the 8/21 call. Breakfast lines on that form (Blueberry Chex, Berry Juice, Goldfish Graham, Pop Tart) are a separate order - confirm they are not expected here.</t>
         </is>
@@ -4267,7 +4607,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rate is $86/hr on ALL clock time - drive, stop, load, unload. No per-stop fee. 3 stops = 1 hr = $86.</t>
+          <t>Contracted $86/hr on ALL clock time - drive, stop, load, unload. No per-stop fee. 3 stops = 1 hr = $86. Run covers 12 TPS schools + 2 SLA Toledo stops.</t>
         </is>
       </c>
     </row>
@@ -4307,11 +4647,11 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>10.38 billable h x $86/hr</t>
+          <t>11.31 billable h x $86/hr</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>892.9400000000001</v>
+        <v>972.37</v>
       </c>
       <c r="D6" s="15" t="n">
         <v>1</v>
@@ -4330,14 +4670,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12 stops x 20 min = 4.00 h</t>
+          <t>14 stops x 20 min = 4.67 h</t>
         </is>
       </c>
       <c r="C7" s="17" t="n">
-        <v>344</v>
+        <v>401.33</v>
       </c>
       <c r="D7" s="18" t="n">
-        <v>0.3852</v>
+        <v>0.4127</v>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
@@ -4372,7 +4712,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr"/>
       <c r="C9" s="19" t="n">
-        <v>892.9400000000001</v>
+        <v>972.37</v>
       </c>
       <c r="D9" s="20" t="n">
         <v>1</v>
@@ -4394,14 +4734,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>255.1 mi / 10 mpg x $5.181</t>
+          <t>257.8 mi / 10 mpg x $5.181</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>132.17</v>
+        <v>133.57</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>0.148</v>
+        <v>0.1374</v>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
@@ -4417,11 +4757,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10.38 h x 0.5 gal/h x $5.181</t>
+          <t>11.31 h x 0.5 gal/h x $5.181</t>
         </is>
       </c>
       <c r="C13" s="17" t="n">
-        <v>26.9</v>
+        <v>29.29</v>
       </c>
       <c r="D13" s="18" t="n">
         <v>0.0301</v>
@@ -4440,11 +4780,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10.38 h x $25 x 1.18</t>
+          <t>11.31 h x $25 x 1.18</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>306.3</v>
+        <v>333.55</v>
       </c>
       <c r="D14" s="18" t="n">
         <v>0.343</v>
@@ -4470,7 +4810,7 @@
         <v>52</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>0.0582</v>
+        <v>0.0535</v>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
@@ -4486,14 +4826,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>255.1 mi x $0.18</t>
+          <t>257.8 mi x $0.18</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>45.92</v>
+        <v>46.4</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>0.0514</v>
+        <v>0.0477</v>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
@@ -4516,7 +4856,7 @@
         <v>30</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>0.0336</v>
+        <v>0.0309</v>
       </c>
       <c r="E17" s="12" t="inlineStr"/>
     </row>
@@ -4528,10 +4868,10 @@
       </c>
       <c r="B18" s="9" t="inlineStr"/>
       <c r="C18" s="19" t="n">
-        <v>593.28</v>
+        <v>624.8099999999999</v>
       </c>
       <c r="D18" s="20" t="n">
-        <v>0.6644</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
@@ -4547,10 +4887,10 @@
       </c>
       <c r="B19" s="13" t="inlineStr"/>
       <c r="C19" s="14" t="n">
-        <v>299.66</v>
+        <v>347.57</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>0.3356</v>
+        <v>0.3574</v>
       </c>
       <c r="E19" s="16" t="inlineStr">
         <is>
@@ -4580,7 +4920,7 @@
         <v>67</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>0.075</v>
+        <v>0.0689</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -4603,7 +4943,7 @@
         <v>85</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
@@ -4626,7 +4966,7 @@
         <v>6</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>0.0067</v>
+        <v>0.0062</v>
       </c>
       <c r="E23" s="12" t="inlineStr"/>
     </row>
@@ -4645,7 +4985,7 @@
         <v>45</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>0.0504</v>
+        <v>0.0463</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -4664,7 +5004,7 @@
         <v>203</v>
       </c>
       <c r="D25" s="20" t="n">
-        <v>0.2273</v>
+        <v>0.2088</v>
       </c>
       <c r="E25" s="21" t="inlineStr"/>
     </row>
@@ -4676,10 +5016,10 @@
       </c>
       <c r="B26" s="9" t="inlineStr"/>
       <c r="C26" s="19" t="n">
-        <v>796.28</v>
+        <v>827.8099999999999</v>
       </c>
       <c r="D26" s="20" t="n">
-        <v>0.8918</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="E26" s="21" t="inlineStr"/>
     </row>
@@ -4691,10 +5031,10 @@
       </c>
       <c r="B27" s="13" t="inlineStr"/>
       <c r="C27" s="14" t="n">
-        <v>96.66</v>
+        <v>144.57</v>
       </c>
       <c r="D27" s="15" t="n">
-        <v>0.1082</v>
+        <v>0.1487</v>
       </c>
       <c r="E27" s="16" t="inlineStr">
         <is>
@@ -4717,7 +5057,7 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" s="17" t="n">
-        <v>3.5</v>
+        <v>3.77</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" s="12" t="inlineStr">
@@ -4734,12 +5074,12 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" s="17" t="n">
-        <v>74.41</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Revenue per school served</t>
+          <t>Revenue per stop across 14 stops</t>
         </is>
       </c>
     </row>
@@ -4751,12 +5091,12 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" s="17" t="n">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>294 cases</t>
+          <t>294 TPS + 14 SLA cases</t>
         </is>
       </c>
     </row>
@@ -4768,7 +5108,7 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" s="17" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" s="12" t="inlineStr">
@@ -4785,7 +5125,7 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" s="17" t="n">
-        <v>76.69</v>
+        <v>73.20999999999999</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" s="12" t="inlineStr">
@@ -4802,7 +5142,7 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" s="17" t="n">
-        <v>9.31</v>
+        <v>12.79</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" s="12" t="inlineStr">
@@ -4822,7 +5162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5004,29 +5344,29 @@
       <c r="A10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>Blocking</t>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Sean</t>
+          <t>BJ</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Rate agreed in writing</t>
+          <t>Confirmed receiving windows</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>$86/hr on all clock time is SupplyNow's structure. Nothing is agreed with SNAP. At 10.38 billable hours that is $892.94.</t>
+          <t>The schedule assumes kitchens take product from 07:00. If the first school cannot receive until 08:00 the whole day shifts and the 13:59 return moves with it.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Before Wed</t>
+          <t>Mon 8/24</t>
         </is>
       </c>
     </row>
@@ -5041,17 +5381,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>BJ</t>
+          <t>BJ / Sean</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Confirmed receiving windows</t>
+          <t>Does the TPS order include breakfast items</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>The schedule assumes kitchens take product from 07:00. If the first school cannot receive until 08:00 the whole day shifts and the 13:59 return moves with it.</t>
+          <t>The 8/21 production form carries Blueberry Chex, Berry Juice, Goldfish Graham and Pop Tart alongside the burger meal. Sean said no milk and no secondary items for TPS - confirm breakfast is excluded or the case count changes.</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -5071,17 +5411,17 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>BJ / Sean</t>
+          <t>BJ</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Does the TPS order include breakfast items</t>
+          <t>All six meal components ship complete</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>The 8/21 production form carries Blueberry Chex, Berry Juice, Goldfish Graham and Pop Tart alongside the burger meal. Sean said no milk and no secondary items for TPS - confirm breakfast is excluded or the case count changes.</t>
+          <t>Production form shows patty, bun, tots, baked beans, watermelon applesauce and ketchup/mustard PC. An incomplete meal at a school is a failed delivery.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -5101,22 +5441,22 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>BJ</t>
+          <t>Sean</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>All six meal components ship complete</t>
+          <t>TPS district delivery pass or vendor check-in</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Production form shows patty, bun, tots, baked beans, watermelon applesauce and ketchup/mustard PC. An incomplete meal at a school is a failed delivery.</t>
+          <t>Some districts require a pass or badge before a driver can enter a building. Unknown for TPS.</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Mon 8/24</t>
+          <t>Tue 8/25</t>
         </is>
       </c>
     </row>
@@ -5131,22 +5471,22 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Sean</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>TPS district delivery pass or vendor check-in</t>
+          <t>Tuesday-night load-out window</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Some districts require a pass or badge before a driver can enter a building. Unknown for TPS.</t>
+          <t>Sean offered a Tuesday night load with overnight hold in the reefer. Need the window and who opens the building.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Tue 8/25</t>
+          <t>Mon 8/24</t>
         </is>
       </c>
     </row>
@@ -5154,29 +5494,29 @@
       <c r="A15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Tuesday-night load-out window</t>
+          <t>SLA Toledo rides on the same truck</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Sean offered a Tuesday night load with overnight hold in the reefer. Need the window and who opens the building.</t>
+          <t>14 SLA cases build a 24 in pallet; school pallets are 33 in. Double-stacked that is 57 in against ~90 in of interior. Combining costs 2.7 mi and 56 min and returns $47.91 more profit than a second truck.</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Mon 8/24</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5191,22 +5531,22 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Mike / Sean</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>SLA Toledo coverage on 8/26</t>
+          <t>Driver assignment</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>SLA has its own delivery that morning and the school truck has no thirteenth floor position. It needs a second vehicle or its cases move to the Monday or Thursday SLA runs.</t>
+          <t>Twelve POD-required school drops in an unfamiliar city on a 10.38 hour day. The truck is not the constraint; the driver is.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Mon 8/24</t>
+          <t>Tue 8/25</t>
         </is>
       </c>
     </row>
@@ -5214,29 +5554,29 @@
       <c r="A17" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Driver assignment</t>
+          <t>No duplicate addresses</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Twelve POD-required school drops in an unfamiliar city on a 10.38 hour day. The truck is not the constraint; the driver is.</t>
+          <t>All 12 street addresses are distinct and no two schools share a building. Checked across street number, street and ZIP.</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Tue 8/25</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5256,12 +5596,12 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>No duplicate addresses</t>
+          <t>Byrnedale vs Glendale-Feilbach name collision</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>All 12 street addresses are distinct and no two schools share a building. Checked across street number, street and ZIP.</t>
+          <t>Byrnedale is AT 3635 Glendale Ave. Glendale-Feilbach is at 2317 Cass Rd. Both in 43614. High risk of a driver or a pallet going to the wrong one - label by school number.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -5286,12 +5626,12 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Byrnedale vs Glendale-Feilbach name collision</t>
+          <t>School name changes</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Byrnedale is AT 3635 Glendale Ave. Glendale-Feilbach is at 2317 Cass Rd. Both in 43614. High risk of a driver or a pallet going to the wrong one - label by school number.</t>
+          <t>TPS now lists Hawkins as Hawkins STEMM Academy and Marshall as Marshall STEMM Academy, and spells Crossgate as Crossgates.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -5316,45 +5656,15 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>School name changes</t>
+          <t>Origin, menu, temperature, pallet method</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>TPS now lists Hawkins as Hawkins STEMM Academy and Marshall as Marshall STEMM Academy, and spells Crossgate as Crossgates.</t>
+          <t>SNAP E 55th; hamburger meal, no milk; refrigerated not frozen; one school per pallet. All settled on the 8/21 call.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Origin, menu, temperature, pallet method</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>SNAP E 55th; hamburger meal, no milk; refrigerated not frozen; one school per pallet. All settled on the 8/21 call.</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Done</t>
         </is>

--- a/toledo-tps/Toledo_TPS_8-26_Workbook.xlsx
+++ b/toledo-tps/Toledo_TPS_8-26_Workbook.xlsx
@@ -85,12 +85,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBEFDC"/>
+        <fgColor rgb="FFE0F0E8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE0F0E8"/>
+        <fgColor rgb="FFFBEFDC"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -146,13 +146,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4587,7 +4594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5086,70 +5093,645 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Effective $/case</t>
+          <t>Marginal profit per added stop</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" s="17" t="n">
-        <v>3.16</v>
+        <v>19.49</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>294 TPS + 14 SLA cases</t>
+          <t>On a run already going to Toledo: +$32.54 revenue, +$13.05 cost</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Effective $/meal</t>
+          <t>Effective $/case</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" s="17" t="n">
-        <v>0.3</v>
+        <v>3.16</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>3,230 estimated meals</t>
+          <t>294 TPS + 14 SLA cases</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cost per billable hour</t>
+          <t>Effective $/meal</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" s="17" t="n">
-        <v>73.20999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Break-even hourly rate</t>
+          <t>3,230 estimated meals</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Margin of safety on rate</t>
+          <t>Cost per billable hour</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" s="17" t="n">
-        <v>12.79</v>
+        <v>73.20999999999999</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" s="12" t="inlineStr">
         <is>
+          <t>Break-even hourly rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Margin of safety on rate</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" s="17" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
           <t>$ per hour the rate can drop before the run loses money</t>
         </is>
       </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>SLA TOLEDO AS A STANDALONE RUN - Mon / Wed / Fri, 2 stops</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Gross sales</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>6.18 h x $86 (1.00 load + 4.52 drive + 0.67 stop)</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="n">
+        <v>531.77</v>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Total controllables</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" s="17" t="n">
+        <v>440.22</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>0.8278</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>Contribution margin</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr"/>
+      <c r="C41" s="19" t="n">
+        <v>91.55</v>
+      </c>
+      <c r="D41" s="20" t="n">
+        <v>0.1722</v>
+      </c>
+      <c r="E41" s="9" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Fixed &amp; allocated</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1 day</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>203</v>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>0.3817</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Total cost</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" s="17" t="n">
+        <v>643.22</v>
+      </c>
+      <c r="D43" s="18" t="n">
+        <v>1.2096</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>OPERATING PROFIT</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr"/>
+      <c r="C44" s="19" t="n">
+        <v>-111.45</v>
+      </c>
+      <c r="D44" s="20" t="n">
+        <v>-0.2096</v>
+      </c>
+      <c r="E44" s="9" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Break-even hourly rate</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" s="17" t="n">
+        <v>104.03</v>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>$18.03/hr above the contracted rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Shortfall per run</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" s="17" t="n">
+        <v>-111.45</v>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>Two stops cannot carry the Cleveland deadhead</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Mon/Wed/Fri standalone, per week</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" s="17" t="n">
+        <v>-334.36</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>Three runs</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Mon+Fri only, Wed rides with the school run</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" s="17" t="n">
+        <v>-222.91</v>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>What the 8/26 combine already saves</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Consolidated to one delivery a week</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" s="17" t="n">
+        <v>-111.45</v>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>Sean floated this and said they have not got it together</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>STOPS NEEDED FOR A TOLEDO RUN TO PAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>Stops</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="C52" s="22" t="inlineStr">
+        <is>
+          <t>Billable h</t>
+        </is>
+      </c>
+      <c r="D52" s="22" t="inlineStr">
+        <is>
+          <t>Gross</t>
+        </is>
+      </c>
+      <c r="E52" s="22" t="inlineStr">
+        <is>
+          <t>Total cost</t>
+        </is>
+      </c>
+      <c r="F52" s="22" t="inlineStr">
+        <is>
+          <t>Operating profit</t>
+        </is>
+      </c>
+      <c r="G52" s="22" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B53" s="23" t="n">
+        <v>228.9</v>
+      </c>
+      <c r="C53" s="23" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="D53" s="24" t="n">
+        <v>531.77</v>
+      </c>
+      <c r="E53" s="24" t="n">
+        <v>643.22</v>
+      </c>
+      <c r="F53" s="24" t="n">
+        <v>-111.45</v>
+      </c>
+      <c r="G53" s="25" t="n">
+        <v>-0.2096</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B54" s="23" t="n">
+        <v>230.2</v>
+      </c>
+      <c r="C54" s="23" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="D54" s="24" t="n">
+        <v>564.3</v>
+      </c>
+      <c r="E54" s="24" t="n">
+        <v>656.27</v>
+      </c>
+      <c r="F54" s="24" t="n">
+        <v>-91.97</v>
+      </c>
+      <c r="G54" s="25" t="n">
+        <v>-0.163</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B55" s="23" t="n">
+        <v>231.5</v>
+      </c>
+      <c r="C55" s="23" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D55" s="24" t="n">
+        <v>596.84</v>
+      </c>
+      <c r="E55" s="24" t="n">
+        <v>669.3200000000001</v>
+      </c>
+      <c r="F55" s="24" t="n">
+        <v>-72.48</v>
+      </c>
+      <c r="G55" s="25" t="n">
+        <v>-0.1214</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B56" s="23" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="C56" s="23" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="D56" s="24" t="n">
+        <v>629.38</v>
+      </c>
+      <c r="E56" s="24" t="n">
+        <v>682.37</v>
+      </c>
+      <c r="F56" s="24" t="n">
+        <v>-52.99</v>
+      </c>
+      <c r="G56" s="25" t="n">
+        <v>-0.0842</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="B57" s="23" t="n">
+        <v>234.1</v>
+      </c>
+      <c r="C57" s="23" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="D57" s="24" t="n">
+        <v>661.91</v>
+      </c>
+      <c r="E57" s="24" t="n">
+        <v>695.42</v>
+      </c>
+      <c r="F57" s="24" t="n">
+        <v>-33.5</v>
+      </c>
+      <c r="G57" s="25" t="n">
+        <v>-0.0506</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B58" s="23" t="n">
+        <v>235.4</v>
+      </c>
+      <c r="C58" s="23" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="D58" s="24" t="n">
+        <v>694.45</v>
+      </c>
+      <c r="E58" s="24" t="n">
+        <v>708.46</v>
+      </c>
+      <c r="F58" s="24" t="n">
+        <v>-14.01</v>
+      </c>
+      <c r="G58" s="25" t="n">
+        <v>-0.0202</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="B59" s="26" t="n">
+        <v>236.7</v>
+      </c>
+      <c r="C59" s="26" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="D59" s="27" t="n">
+        <v>726.99</v>
+      </c>
+      <c r="E59" s="27" t="n">
+        <v>721.51</v>
+      </c>
+      <c r="F59" s="27" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="G59" s="28" t="n">
+        <v>0.0075</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="B60" s="26" t="n">
+        <v>238</v>
+      </c>
+      <c r="C60" s="26" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="D60" s="27" t="n">
+        <v>759.52</v>
+      </c>
+      <c r="E60" s="27" t="n">
+        <v>734.5599999999999</v>
+      </c>
+      <c r="F60" s="27" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="G60" s="28" t="n">
+        <v>0.0329</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="B61" s="26" t="n">
+        <v>239.3</v>
+      </c>
+      <c r="C61" s="26" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="D61" s="27" t="n">
+        <v>792.0599999999999</v>
+      </c>
+      <c r="E61" s="27" t="n">
+        <v>747.61</v>
+      </c>
+      <c r="F61" s="27" t="n">
+        <v>44.45</v>
+      </c>
+      <c r="G61" s="28" t="n">
+        <v>0.0561</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="B62" s="26" t="n">
+        <v>240.6</v>
+      </c>
+      <c r="C62" s="26" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="D62" s="27" t="n">
+        <v>824.6</v>
+      </c>
+      <c r="E62" s="27" t="n">
+        <v>760.66</v>
+      </c>
+      <c r="F62" s="27" t="n">
+        <v>63.94</v>
+      </c>
+      <c r="G62" s="28" t="n">
+        <v>0.0775</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="B63" s="26" t="n">
+        <v>241.9</v>
+      </c>
+      <c r="C63" s="26" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="D63" s="27" t="n">
+        <v>857.13</v>
+      </c>
+      <c r="E63" s="27" t="n">
+        <v>773.71</v>
+      </c>
+      <c r="F63" s="27" t="n">
+        <v>83.43000000000001</v>
+      </c>
+      <c r="G63" s="28" t="n">
+        <v>0.0973</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="B64" s="26" t="n">
+        <v>243.2</v>
+      </c>
+      <c r="C64" s="26" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="D64" s="27" t="n">
+        <v>889.67</v>
+      </c>
+      <c r="E64" s="27" t="n">
+        <v>786.75</v>
+      </c>
+      <c r="F64" s="27" t="n">
+        <v>102.92</v>
+      </c>
+      <c r="G64" s="28" t="n">
+        <v>0.1157</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="B65" s="26" t="n">
+        <v>244.5</v>
+      </c>
+      <c r="C65" s="26" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="D65" s="27" t="n">
+        <v>922.21</v>
+      </c>
+      <c r="E65" s="27" t="n">
+        <v>799.8</v>
+      </c>
+      <c r="F65" s="27" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="G65" s="28" t="n">
+        <v>0.1327</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>Marginal stop on a Toledo-bound run</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr"/>
+      <c r="C66" s="9" t="inlineStr"/>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>+$32.54 revenue</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>+$13.05 cost</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>+$19.49 profit</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5224,7 +5806,7 @@
       <c r="A6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -5254,7 +5836,7 @@
       <c r="A7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -5284,7 +5866,7 @@
       <c r="A8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -5314,7 +5896,7 @@
       <c r="A9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -5344,7 +5926,7 @@
       <c r="A10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5374,7 +5956,7 @@
       <c r="A11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5404,7 +5986,7 @@
       <c r="A12" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5434,7 +6016,7 @@
       <c r="A13" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5464,7 +6046,7 @@
       <c r="A14" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5494,7 +6076,7 @@
       <c r="A15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -5524,7 +6106,7 @@
       <c r="A16" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5554,7 +6136,7 @@
       <c r="A17" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -5584,7 +6166,7 @@
       <c r="A18" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -5614,7 +6196,7 @@
       <c r="A19" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -5644,7 +6226,7 @@
       <c r="A20" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>

--- a/toledo-tps/Toledo_TPS_8-26_Workbook.xlsx
+++ b/toledo-tps/Toledo_TPS_8-26_Workbook.xlsx
@@ -80,12 +80,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBE7E3"/>
+        <fgColor rgb="FFE0F0E8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE0F0E8"/>
+        <fgColor rgb="FFFBE7E3"/>
       </patternFill>
     </fill>
     <fill>
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,16 +150,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2951,7 +2948,7 @@
       <c r="A6" s="7" t="inlineStr"/>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>DEADHEAD OUT - SNAP E 55th Cleveland to west Toledo</t>
+          <t>TRANSIT OUT (billable) - SNAP E 55th Cleveland to west Toledo</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -3577,7 +3574,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>DEADHEAD BACK - east Toledo to SNAP E 55th</t>
+          <t>TRANSIT BACK (billable) - east Toledo to SNAP E 55th</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr"/>
@@ -3606,7 +3603,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Outbound deadhead</t>
+          <t>Transit out, billable</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -3648,7 +3645,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Return deadhead</t>
+          <t>Transit back, billable</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -4594,7 +4591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4607,14 +4604,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TAB 5 - INTERNAL PRICE COMP</t>
+          <t>TAB 5 - PRICE VS COST</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Contracted $86/hr on ALL clock time - drive, stop, load, unload. No per-stop fee. 3 stops = 1 hr = $86. Run covers 12 TPS schools + 2 SLA Toledo stops.</t>
+          <t>Charge vs the cost of putting a truck and a driver on the road. $86/hr on ALL clock time - drive, stop, load, unload. Truck note, insurance, plates and office are paid whether this truck rolls or not and are not charged to the run.</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4633,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>% of revenue</t>
+          <t>% of charge</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -4649,7 +4646,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>GROSS SALES</t>
+          <t>CHARGE</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -4665,7 +4662,7 @@
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>All clock time. Load-out 1.00 + drive 5.38 + stop 4.00.</t>
+          <t>All clock time: 1.00 load + 5.64 drive + 4.67 stop</t>
         </is>
       </c>
     </row>
@@ -4688,1050 +4685,806 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>3 stops = 1 hour = $86</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Less allowances</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>3 stops = 1 hour = $86 - the cheapest hours on the run</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>NET SALES</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr"/>
-      <c r="C9" s="19" t="n">
-        <v>972.37</v>
-      </c>
-      <c r="D9" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="21" t="inlineStr"/>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>COST TO PUT THE TRUCK AND DRIVER OUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Fuel</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>257.8 mi / 10 mpg x $5.181</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>133.57</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>0.1374</v>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>PADD 2 on-highway, week of 8/10/26</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>CONTROLLABLES</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Reefer fuel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>11.31 h x 0.5 gal/h x $5.181</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>29.29</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Running refrigerated the whole shift</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Fuel</t>
+          <t xml:space="preserve">  Driver wages + burden</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>257.8 mi / 10 mpg x $5.181</t>
+          <t>11.31 h x $25 x 1.18</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>133.57</v>
+        <v>333.55</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>0.1374</v>
+        <v>0.343</v>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>PADD 2 on-highway, week of 8/10/26</t>
+          <t>On-duty hours - load-out, drive and stop time in one line</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Reefer fuel</t>
+          <t xml:space="preserve">  Tolls</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11.31 h x 0.5 gal/h x $5.181</t>
+          <t>Ohio Turnpike round trip</t>
         </is>
       </c>
       <c r="C13" s="17" t="n">
-        <v>29.29</v>
+        <v>52</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>0.0301</v>
+        <v>0.0535</v>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Running refrigerated the whole shift</t>
+          <t>Estimate - replace with actual</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Driver wages + burden</t>
+          <t xml:space="preserve">  Tires &amp; maintenance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11.31 h x $25 x 1.18</t>
+          <t>257.8 mi x $0.18</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>333.55</v>
+        <v>46.4</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>0.343</v>
+        <v>0.0477</v>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>On-duty hours - load-out, drive and stop time in one line</t>
+          <t>Accrues with the miles</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tolls</t>
+          <t xml:space="preserve">  Per diem</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ohio Turnpike round trip</t>
+          <t>Driver meal</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>0.0535</v>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>Estimate - replace with actual</t>
-        </is>
-      </c>
+        <v>0.0309</v>
+      </c>
+      <c r="E15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Maintenance &amp; tire reserve</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>257.8 mi x $0.18</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>0.0477</v>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>Fleet reserve, not a cash cost on the day</t>
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Total cost out</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr"/>
+      <c r="C16" s="19" t="n">
+        <v>624.8099999999999</v>
+      </c>
+      <c r="D16" s="20" t="n">
+        <v>0.6425999999999999</v>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>Wages, fuel, tolls, tires, per diem</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Per diem</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Driver meal</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>0.0309</v>
-      </c>
-      <c r="E17" s="12" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Total controllables</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr"/>
-      <c r="C18" s="19" t="n">
-        <v>624.8099999999999</v>
-      </c>
-      <c r="D18" s="20" t="n">
-        <v>0.6425999999999999</v>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
-        <is>
-          <t>Costs that move with the run</t>
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>MARGIN</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr"/>
+      <c r="C17" s="14" t="n">
+        <v>347.57</v>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>Charge less the cost of putting a truck and a driver out</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>CONTRIBUTION MARGIN</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr"/>
-      <c r="C19" s="14" t="n">
-        <v>347.57</v>
-      </c>
-      <c r="D19" s="15" t="n">
-        <v>0.3574</v>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>What a marginal load is worth taking for</t>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>UNIT ECONOMICS</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>FIXED &amp; ALLOCATED</t>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Charged $/mile</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" s="17" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>257.8 miles, all of them on the clock</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Truck lease / depreciation</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1 day</t>
-        </is>
-      </c>
+          <t>Charged $/stop</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" s="17" t="n">
-        <v>67</v>
-      </c>
-      <c r="D21" s="18" t="n">
-        <v>0.0689</v>
-      </c>
+        <v>69.45999999999999</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>~$1,400/mo over 21 working days</t>
+          <t>Across 14 stops</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Insurance</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1 day</t>
-        </is>
-      </c>
+          <t>Margin per added stop</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" s="17" t="n">
-        <v>85</v>
-      </c>
-      <c r="D22" s="18" t="n">
-        <v>0.08740000000000001</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Liability, cargo, physical damage</t>
+          <t>On a truck already going to Toledo: +$28.67 charged, about $10 of cost</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ELD &amp; telematics</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1 day</t>
-        </is>
-      </c>
+          <t>Charged $/case</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>0.0062</v>
-      </c>
-      <c r="E23" s="12" t="inlineStr"/>
+        <v>3.16</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>294 TPS + 14 SLA cases</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Admin overhead</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1 day</t>
-        </is>
-      </c>
+          <t>Charged $/meal</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" s="17" t="n">
-        <v>45</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>0.0463</v>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Dispatch, billing, phone</t>
+          <t>3,230 estimated meals</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>Total fixed</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr"/>
-      <c r="C25" s="19" t="n">
-        <v>203</v>
-      </c>
-      <c r="D25" s="20" t="n">
-        <v>0.2088</v>
-      </c>
-      <c r="E25" s="21" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Cost per billable hour</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" s="17" t="n">
+        <v>55.26</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>What it costs to have the truck out, per hour</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>TOTAL COST</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr"/>
-      <c r="C26" s="19" t="n">
-        <v>827.8099999999999</v>
-      </c>
-      <c r="D26" s="20" t="n">
-        <v>0.8512999999999999</v>
-      </c>
-      <c r="E26" s="21" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>OPERATING PROFIT</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr"/>
-      <c r="C27" s="14" t="n">
-        <v>144.57</v>
-      </c>
-      <c r="D27" s="15" t="n">
-        <v>0.1487</v>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>After the truck, insurance and overhead carry their share</t>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Margin per billable hour</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" s="17" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>What each billable hour keeps</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>SLA TOLEDO AS A STANDALONE RUN - Mon / Wed / Fri, 2 stops</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>UNIT ECONOMICS</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>6.18 h x $86 (1.00 load + 4.52 drive + 0.67 stop)</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="n">
+        <v>531.77</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Effective $/mile</t>
+          <t>Total cost out</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" s="17" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>255.1 miles, 94% of them deadhead</t>
-        </is>
-      </c>
+        <v>440.22</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>0.8278</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Effective $/stop</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" s="17" t="n">
-        <v>69.45999999999999</v>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>Revenue per stop across 14 stops</t>
-        </is>
-      </c>
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>MARGIN</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr"/>
+      <c r="C31" s="19" t="n">
+        <v>91.55</v>
+      </c>
+      <c r="D31" s="20" t="n">
+        <v>0.1722</v>
+      </c>
+      <c r="E31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Marginal profit per added stop</t>
+          <t>Margin per billable hour</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" s="17" t="n">
-        <v>19.49</v>
+        <v>14.81</v>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>On a run already going to Toledo: +$32.54 revenue, +$13.05 cost</t>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>vs $30.73/h on the 14-stop run</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Effective $/case</t>
+          <t>Margin per run</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" s="17" t="n">
-        <v>3.16</v>
+        <v>91.55</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>294 TPS + 14 SLA cases</t>
+          <t>Two stops carry the whole road themselves</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Effective $/meal</t>
+          <t>Mon/Wed/Fri, per week</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" s="17" t="n">
-        <v>0.3</v>
+        <v>274.64</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>3,230 estimated meals</t>
+          <t>Three runs</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cost per billable hour</t>
+          <t>Same two stops added to a school run</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" s="17" t="n">
-        <v>73.20999999999999</v>
+        <v>58</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Break-even hourly rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Margin of safety on rate</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" s="17" t="n">
-        <v>12.79</v>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" s="12" t="inlineStr">
-        <is>
-          <t>$ per hour the rate can drop before the run loses money</t>
+          <t>+0.67 h and +2.7 mi on a truck already going, against about $21 of cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>STOPS AGAINST MARGIN ON A TOLEDO RUN</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>SLA TOLEDO AS A STANDALONE RUN - Mon / Wed / Fri, 2 stops</t>
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>Stops</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>Billable h</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>Cost out</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr">
+        <is>
+          <t>Margin %</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Gross sales</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>6.18 h x $86 (1.00 load + 4.52 drive + 0.67 stop)</t>
-        </is>
-      </c>
-      <c r="C39" s="17" t="n">
+      <c r="A39" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B39" s="23" t="n">
+        <v>228.9</v>
+      </c>
+      <c r="C39" s="23" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="D39" s="24" t="n">
         <v>531.77</v>
       </c>
-      <c r="D39" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" s="24" t="n">
+        <v>440.22</v>
+      </c>
+      <c r="F39" s="24" t="n">
+        <v>91.55</v>
+      </c>
+      <c r="G39" s="25" t="n">
+        <v>0.1722</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Total controllables</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" s="17" t="n">
-        <v>440.22</v>
-      </c>
-      <c r="D40" s="18" t="n">
-        <v>0.8278</v>
-      </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="A40" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B40" s="23" t="n">
+        <v>230.2</v>
+      </c>
+      <c r="C40" s="23" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="D40" s="24" t="n">
+        <v>564.3</v>
+      </c>
+      <c r="E40" s="24" t="n">
+        <v>453.27</v>
+      </c>
+      <c r="F40" s="24" t="n">
+        <v>111.03</v>
+      </c>
+      <c r="G40" s="25" t="n">
+        <v>0.1968</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>Contribution margin</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr"/>
-      <c r="C41" s="19" t="n">
-        <v>91.55</v>
-      </c>
-      <c r="D41" s="20" t="n">
-        <v>0.1722</v>
-      </c>
-      <c r="E41" s="9" t="inlineStr"/>
+      <c r="A41" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B41" s="23" t="n">
+        <v>231.5</v>
+      </c>
+      <c r="C41" s="23" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D41" s="24" t="n">
+        <v>596.84</v>
+      </c>
+      <c r="E41" s="24" t="n">
+        <v>466.32</v>
+      </c>
+      <c r="F41" s="24" t="n">
+        <v>130.52</v>
+      </c>
+      <c r="G41" s="25" t="n">
+        <v>0.2187</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Fixed &amp; allocated</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>1 day</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="n">
-        <v>203</v>
-      </c>
-      <c r="D42" s="18" t="n">
-        <v>0.3817</v>
-      </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="A42" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B42" s="23" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="C42" s="23" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="D42" s="24" t="n">
+        <v>629.38</v>
+      </c>
+      <c r="E42" s="24" t="n">
+        <v>479.37</v>
+      </c>
+      <c r="F42" s="24" t="n">
+        <v>150.01</v>
+      </c>
+      <c r="G42" s="25" t="n">
+        <v>0.2383</v>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Total cost</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" s="17" t="n">
-        <v>643.22</v>
-      </c>
-      <c r="D43" s="18" t="n">
-        <v>1.2096</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="A43" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="B43" s="23" t="n">
+        <v>234.1</v>
+      </c>
+      <c r="C43" s="23" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="D43" s="24" t="n">
+        <v>661.91</v>
+      </c>
+      <c r="E43" s="24" t="n">
+        <v>492.42</v>
+      </c>
+      <c r="F43" s="24" t="n">
+        <v>169.5</v>
+      </c>
+      <c r="G43" s="25" t="n">
+        <v>0.2561</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>OPERATING PROFIT</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr"/>
-      <c r="C44" s="19" t="n">
-        <v>-111.45</v>
-      </c>
-      <c r="D44" s="20" t="n">
-        <v>-0.2096</v>
-      </c>
-      <c r="E44" s="9" t="inlineStr"/>
+      <c r="A44" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B44" s="23" t="n">
+        <v>235.4</v>
+      </c>
+      <c r="C44" s="23" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="D44" s="24" t="n">
+        <v>694.45</v>
+      </c>
+      <c r="E44" s="24" t="n">
+        <v>505.46</v>
+      </c>
+      <c r="F44" s="24" t="n">
+        <v>188.99</v>
+      </c>
+      <c r="G44" s="25" t="n">
+        <v>0.2721</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Break-even hourly rate</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" s="17" t="n">
-        <v>104.03</v>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>$18.03/hr above the contracted rate</t>
-        </is>
+      <c r="A45" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="B45" s="23" t="n">
+        <v>236.7</v>
+      </c>
+      <c r="C45" s="23" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="D45" s="24" t="n">
+        <v>726.99</v>
+      </c>
+      <c r="E45" s="24" t="n">
+        <v>518.51</v>
+      </c>
+      <c r="F45" s="24" t="n">
+        <v>208.47</v>
+      </c>
+      <c r="G45" s="25" t="n">
+        <v>0.2868</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Shortfall per run</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" s="17" t="n">
-        <v>-111.45</v>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" s="12" t="inlineStr">
-        <is>
-          <t>Two stops cannot carry the Cleveland deadhead</t>
-        </is>
+      <c r="A46" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="B46" s="23" t="n">
+        <v>238</v>
+      </c>
+      <c r="C46" s="23" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="D46" s="24" t="n">
+        <v>759.52</v>
+      </c>
+      <c r="E46" s="24" t="n">
+        <v>531.5599999999999</v>
+      </c>
+      <c r="F46" s="24" t="n">
+        <v>227.96</v>
+      </c>
+      <c r="G46" s="25" t="n">
+        <v>0.3001</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Mon/Wed/Fri standalone, per week</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" s="17" t="n">
-        <v>-334.36</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" s="12" t="inlineStr">
-        <is>
-          <t>Three runs</t>
-        </is>
+      <c r="A47" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="B47" s="23" t="n">
+        <v>239.3</v>
+      </c>
+      <c r="C47" s="23" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="D47" s="24" t="n">
+        <v>792.0599999999999</v>
+      </c>
+      <c r="E47" s="24" t="n">
+        <v>544.61</v>
+      </c>
+      <c r="F47" s="24" t="n">
+        <v>247.45</v>
+      </c>
+      <c r="G47" s="25" t="n">
+        <v>0.3124</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Mon+Fri only, Wed rides with the school run</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" s="17" t="n">
-        <v>-222.91</v>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" s="12" t="inlineStr">
-        <is>
-          <t>What the 8/26 combine already saves</t>
-        </is>
+      <c r="A48" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B48" s="23" t="n">
+        <v>240.6</v>
+      </c>
+      <c r="C48" s="23" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="D48" s="24" t="n">
+        <v>824.6</v>
+      </c>
+      <c r="E48" s="24" t="n">
+        <v>557.66</v>
+      </c>
+      <c r="F48" s="24" t="n">
+        <v>266.94</v>
+      </c>
+      <c r="G48" s="25" t="n">
+        <v>0.3237</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Consolidated to one delivery a week</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" s="17" t="n">
-        <v>-111.45</v>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" s="12" t="inlineStr">
-        <is>
-          <t>Sean floated this and said they have not got it together</t>
-        </is>
+      <c r="A49" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B49" s="23" t="n">
+        <v>241.9</v>
+      </c>
+      <c r="C49" s="23" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="D49" s="24" t="n">
+        <v>857.13</v>
+      </c>
+      <c r="E49" s="24" t="n">
+        <v>570.71</v>
+      </c>
+      <c r="F49" s="24" t="n">
+        <v>286.43</v>
+      </c>
+      <c r="G49" s="25" t="n">
+        <v>0.3342</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="B50" s="23" t="n">
+        <v>243.2</v>
+      </c>
+      <c r="C50" s="23" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="D50" s="24" t="n">
+        <v>889.67</v>
+      </c>
+      <c r="E50" s="24" t="n">
+        <v>583.75</v>
+      </c>
+      <c r="F50" s="24" t="n">
+        <v>305.92</v>
+      </c>
+      <c r="G50" s="25" t="n">
+        <v>0.3439</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>STOPS NEEDED FOR A TOLEDO RUN TO PAY</t>
-        </is>
+      <c r="A51" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="B51" s="23" t="n">
+        <v>244.5</v>
+      </c>
+      <c r="C51" s="23" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="D51" s="24" t="n">
+        <v>922.21</v>
+      </c>
+      <c r="E51" s="24" t="n">
+        <v>596.8</v>
+      </c>
+      <c r="F51" s="24" t="n">
+        <v>325.4</v>
+      </c>
+      <c r="G51" s="25" t="n">
+        <v>0.3529</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="22" t="inlineStr">
-        <is>
-          <t>Stops</t>
-        </is>
-      </c>
-      <c r="B52" s="22" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="C52" s="22" t="inlineStr">
-        <is>
-          <t>Billable h</t>
-        </is>
-      </c>
-      <c r="D52" s="22" t="inlineStr">
-        <is>
-          <t>Gross</t>
-        </is>
-      </c>
-      <c r="E52" s="22" t="inlineStr">
-        <is>
-          <t>Total cost</t>
-        </is>
-      </c>
-      <c r="F52" s="22" t="inlineStr">
-        <is>
-          <t>Operating profit</t>
-        </is>
-      </c>
-      <c r="G52" s="22" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="B53" s="23" t="n">
-        <v>228.9</v>
-      </c>
-      <c r="C53" s="23" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="D53" s="24" t="n">
-        <v>531.77</v>
-      </c>
-      <c r="E53" s="24" t="n">
-        <v>643.22</v>
-      </c>
-      <c r="F53" s="24" t="n">
-        <v>-111.45</v>
-      </c>
-      <c r="G53" s="25" t="n">
-        <v>-0.2096</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B54" s="23" t="n">
-        <v>230.2</v>
-      </c>
-      <c r="C54" s="23" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="D54" s="24" t="n">
-        <v>564.3</v>
-      </c>
-      <c r="E54" s="24" t="n">
-        <v>656.27</v>
-      </c>
-      <c r="F54" s="24" t="n">
-        <v>-91.97</v>
-      </c>
-      <c r="G54" s="25" t="n">
-        <v>-0.163</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="B55" s="23" t="n">
-        <v>231.5</v>
-      </c>
-      <c r="C55" s="23" t="n">
-        <v>6.94</v>
-      </c>
-      <c r="D55" s="24" t="n">
-        <v>596.84</v>
-      </c>
-      <c r="E55" s="24" t="n">
-        <v>669.3200000000001</v>
-      </c>
-      <c r="F55" s="24" t="n">
-        <v>-72.48</v>
-      </c>
-      <c r="G55" s="25" t="n">
-        <v>-0.1214</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="B56" s="23" t="n">
-        <v>232.8</v>
-      </c>
-      <c r="C56" s="23" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="D56" s="24" t="n">
-        <v>629.38</v>
-      </c>
-      <c r="E56" s="24" t="n">
-        <v>682.37</v>
-      </c>
-      <c r="F56" s="24" t="n">
-        <v>-52.99</v>
-      </c>
-      <c r="G56" s="25" t="n">
-        <v>-0.0842</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="B57" s="23" t="n">
-        <v>234.1</v>
-      </c>
-      <c r="C57" s="23" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="D57" s="24" t="n">
-        <v>661.91</v>
-      </c>
-      <c r="E57" s="24" t="n">
-        <v>695.42</v>
-      </c>
-      <c r="F57" s="24" t="n">
-        <v>-33.5</v>
-      </c>
-      <c r="G57" s="25" t="n">
-        <v>-0.0506</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="B58" s="23" t="n">
-        <v>235.4</v>
-      </c>
-      <c r="C58" s="23" t="n">
-        <v>8.07</v>
-      </c>
-      <c r="D58" s="24" t="n">
-        <v>694.45</v>
-      </c>
-      <c r="E58" s="24" t="n">
-        <v>708.46</v>
-      </c>
-      <c r="F58" s="24" t="n">
-        <v>-14.01</v>
-      </c>
-      <c r="G58" s="25" t="n">
-        <v>-0.0202</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="B59" s="26" t="n">
-        <v>236.7</v>
-      </c>
-      <c r="C59" s="26" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="D59" s="27" t="n">
-        <v>726.99</v>
-      </c>
-      <c r="E59" s="27" t="n">
-        <v>721.51</v>
-      </c>
-      <c r="F59" s="27" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="G59" s="28" t="n">
-        <v>0.0075</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="B60" s="26" t="n">
-        <v>238</v>
-      </c>
-      <c r="C60" s="26" t="n">
-        <v>8.83</v>
-      </c>
-      <c r="D60" s="27" t="n">
-        <v>759.52</v>
-      </c>
-      <c r="E60" s="27" t="n">
-        <v>734.5599999999999</v>
-      </c>
-      <c r="F60" s="27" t="n">
-        <v>24.96</v>
-      </c>
-      <c r="G60" s="28" t="n">
-        <v>0.0329</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="26" t="n">
-        <v>10</v>
-      </c>
-      <c r="B61" s="26" t="n">
-        <v>239.3</v>
-      </c>
-      <c r="C61" s="26" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="D61" s="27" t="n">
-        <v>792.0599999999999</v>
-      </c>
-      <c r="E61" s="27" t="n">
-        <v>747.61</v>
-      </c>
-      <c r="F61" s="27" t="n">
-        <v>44.45</v>
-      </c>
-      <c r="G61" s="28" t="n">
-        <v>0.0561</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="26" t="n">
-        <v>11</v>
-      </c>
-      <c r="B62" s="26" t="n">
-        <v>240.6</v>
-      </c>
-      <c r="C62" s="26" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="D62" s="27" t="n">
-        <v>824.6</v>
-      </c>
-      <c r="E62" s="27" t="n">
-        <v>760.66</v>
-      </c>
-      <c r="F62" s="27" t="n">
-        <v>63.94</v>
-      </c>
-      <c r="G62" s="28" t="n">
-        <v>0.0775</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="B63" s="26" t="n">
-        <v>241.9</v>
-      </c>
-      <c r="C63" s="26" t="n">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="D63" s="27" t="n">
-        <v>857.13</v>
-      </c>
-      <c r="E63" s="27" t="n">
-        <v>773.71</v>
-      </c>
-      <c r="F63" s="27" t="n">
-        <v>83.43000000000001</v>
-      </c>
-      <c r="G63" s="28" t="n">
-        <v>0.0973</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="26" t="n">
-        <v>13</v>
-      </c>
-      <c r="B64" s="26" t="n">
-        <v>243.2</v>
-      </c>
-      <c r="C64" s="26" t="n">
-        <v>10.34</v>
-      </c>
-      <c r="D64" s="27" t="n">
-        <v>889.67</v>
-      </c>
-      <c r="E64" s="27" t="n">
-        <v>786.75</v>
-      </c>
-      <c r="F64" s="27" t="n">
-        <v>102.92</v>
-      </c>
-      <c r="G64" s="28" t="n">
-        <v>0.1157</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="26" t="n">
-        <v>14</v>
-      </c>
-      <c r="B65" s="26" t="n">
-        <v>244.5</v>
-      </c>
-      <c r="C65" s="26" t="n">
-        <v>10.72</v>
-      </c>
-      <c r="D65" s="27" t="n">
-        <v>922.21</v>
-      </c>
-      <c r="E65" s="27" t="n">
-        <v>799.8</v>
-      </c>
-      <c r="F65" s="27" t="n">
-        <v>122.4</v>
-      </c>
-      <c r="G65" s="28" t="n">
-        <v>0.1327</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="9" t="inlineStr">
-        <is>
-          <t>Marginal stop on a Toledo-bound run</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="inlineStr"/>
-      <c r="C66" s="9" t="inlineStr"/>
-      <c r="D66" s="9" t="inlineStr">
-        <is>
-          <t>+$32.54 revenue</t>
-        </is>
-      </c>
-      <c r="E66" s="9" t="inlineStr">
-        <is>
-          <t>+$13.05 cost</t>
-        </is>
-      </c>
-      <c r="F66" s="9" t="inlineStr">
-        <is>
-          <t>+$19.49 profit</t>
-        </is>
-      </c>
-      <c r="G66" s="9" t="inlineStr"/>
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Each stop added to a Toledo truck</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr"/>
+      <c r="C52" s="9" t="inlineStr"/>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>+$28.67 charged</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>~$10 cost</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>about +$19 margin</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5806,7 +5559,7 @@
       <c r="A6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -5836,7 +5589,7 @@
       <c r="A7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -5866,7 +5619,7 @@
       <c r="A8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -5896,7 +5649,7 @@
       <c r="A9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
@@ -5926,7 +5679,7 @@
       <c r="A10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5956,7 +5709,7 @@
       <c r="A11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5986,7 +5739,7 @@
       <c r="A12" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6016,7 +5769,7 @@
       <c r="A13" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6046,7 +5799,7 @@
       <c r="A14" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6076,7 +5829,7 @@
       <c r="A15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="31" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -6106,7 +5859,7 @@
       <c r="A16" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6136,7 +5889,7 @@
       <c r="A17" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="31" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -6166,7 +5919,7 @@
       <c r="A18" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="31" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -6196,7 +5949,7 @@
       <c r="A19" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="31" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -6226,7 +5979,7 @@
       <c r="A20" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="31" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
